--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -795,6 +795,374 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122515128</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56581</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Alträsksvedjan, Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>796235</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7304204</v>
+      </c>
+      <c r="S3" t="n">
+        <v>21</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122515129</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57532</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Alträsksvedjan, Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>796235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7304204</v>
+      </c>
+      <c r="S4" t="n">
+        <v>21</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>122515098</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58008</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102125</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Alträsksvedjan, Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>796235</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7304204</v>
+      </c>
+      <c r="S5" t="n">
+        <v>21</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515128</v>
+        <v>122515093</v>
       </c>
       <c r="B3" t="n">
-        <v>56581</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,31 +814,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -887,7 +877,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +887,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515129</v>
+        <v>122515128</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>56581</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -940,26 +930,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>102612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1062,11 +1052,6 @@
       </c>
       <c r="E5" t="n">
         <v>102125</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Tallbit</t>
-        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,6 +1149,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>122547945</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56592</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102613</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alträsksvedjan, Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>796235</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7304204</v>
+      </c>
+      <c r="S6" t="n">
+        <v>21</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Thomas Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Thomas Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515093</v>
+        <v>122515129</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -816,6 +816,11 @@
       <c r="E3" t="n">
         <v>103021</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -828,7 +833,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -877,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,7 +922,7 @@
         <v>122515128</v>
       </c>
       <c r="B4" t="n">
-        <v>56581</v>
+        <v>56585</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,6 +936,11 @@
       </c>
       <c r="E4" t="n">
         <v>102612</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1038,7 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58008</v>
+        <v>58012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,6 +1062,11 @@
       </c>
       <c r="E5" t="n">
         <v>102125</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallbit</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1154,7 +1169,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>56592</v>
+        <v>56596</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1168,6 +1183,11 @@
       </c>
       <c r="E6" t="n">
         <v>102613</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515129</v>
+        <v>122515093</v>
       </c>
       <c r="B3" t="n">
         <v>57536</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515093</v>
+        <v>122515098</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>58012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,35 +810,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515098</v>
+        <v>122515129</v>
       </c>
       <c r="B5" t="n">
-        <v>58012</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515098</v>
+        <v>122515129</v>
       </c>
       <c r="B3" t="n">
-        <v>58012</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +810,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,7 +922,7 @@
         <v>122515128</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>56586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515129</v>
+        <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>57536</v>
+        <v>58013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,25 +1057,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,7 +1169,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>56596</v>
+        <v>56597</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,7 +798,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515129</v>
+        <v>122515093</v>
       </c>
       <c r="B3" t="n">
         <v>57537</v>
@@ -833,7 +833,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515128</v>
+        <v>122515098</v>
       </c>
       <c r="B4" t="n">
-        <v>56586</v>
+        <v>58013</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,14 +957,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515098</v>
+        <v>122515128</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>56586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,9 +1078,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515093</v>
+        <v>122515128</v>
       </c>
       <c r="B3" t="n">
-        <v>57537</v>
+        <v>56586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,26 +814,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515098</v>
+        <v>122515093</v>
       </c>
       <c r="B4" t="n">
-        <v>58013</v>
+        <v>57537</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,35 +936,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515128</v>
+        <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>56586</v>
+        <v>58013</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1057,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,14 +1083,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -801,7 +801,7 @@
         <v>122515128</v>
       </c>
       <c r="B3" t="n">
-        <v>56586</v>
+        <v>56680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515093</v>
+        <v>122515130</v>
       </c>
       <c r="B4" t="n">
-        <v>57537</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,7 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>58107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>56597</v>
+        <v>56691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515128</v>
+        <v>122515129</v>
       </c>
       <c r="B3" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,31 +814,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -924,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515130</v>
+        <v>122515098</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>58107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,35 +931,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102125</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1018,7 +1013,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515098</v>
+        <v>122515128</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
+        <v>56680</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,20 +1052,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1083,9 +1078,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515098</v>
+        <v>122515128</v>
       </c>
       <c r="B4" t="n">
-        <v>58107</v>
+        <v>56680</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,20 +931,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102125</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -957,9 +957,14 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1003,7 +1008,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1013,7 +1018,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1040,10 +1045,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515128</v>
+        <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>56680</v>
+        <v>58107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,20 +1057,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>102125</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1078,14 +1083,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -798,10 +798,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122515129</v>
+        <v>122515128</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>56680</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,26 +814,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -919,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515128</v>
+        <v>122515129</v>
       </c>
       <c r="B4" t="n">
-        <v>56680</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,31 +940,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1048,12 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58107</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58369</v>
+        <v>58372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58372</v>
+        <v>58375</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1048,7 +1048,7 @@
         <v>122515098</v>
       </c>
       <c r="B5" t="n">
-        <v>58375</v>
+        <v>58376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>57019</v>
+        <v>57045</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>57045</v>
+        <v>57047</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>57047</v>
+        <v>57055</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -1164,7 +1164,7 @@
         <v>122547945</v>
       </c>
       <c r="B6" t="n">
-        <v>57055</v>
+        <v>57056</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66220196</v>
+        <v>122515098</v>
       </c>
       <c r="B2" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>102125</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,11 +708,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -726,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796234.8709434285</v>
+        <v>796235</v>
       </c>
       <c r="R2" t="n">
-        <v>7304203.706247782</v>
+        <v>7304204</v>
       </c>
       <c r="S2" t="n">
         <v>21</v>
@@ -756,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-11</t>
+          <t>2025-02-08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,12 +779,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Sundberg</t>
+          <t>Viktor Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -801,16 +794,11 @@
         <v>122515128</v>
       </c>
       <c r="B3" t="n">
-        <v>56680</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -924,37 +912,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122515129</v>
+        <v>34464875</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>102613</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -962,9 +945,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1003,22 +986,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2010-01-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2010-01-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,39 +1016,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Ulf P Eriksson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Ulf P Eriksson, Jan-Olov Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122515098</v>
+        <v>45113455</v>
       </c>
       <c r="B5" t="n">
-        <v>58377</v>
+        <v>57785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102125</v>
+        <v>102622</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1080,7 +1063,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1119,22 +1102,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2013-04-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2013-04-04</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,59 +1132,58 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Tomas Berlin</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Viktor Persson</t>
+          <t>Tomas Berlin, Jenny Renström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122547945</v>
+        <v>66220196</v>
       </c>
       <c r="B6" t="n">
-        <v>57056</v>
+        <v>58238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102613</v>
+        <v>103012</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>rastande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Alträsksvedjan, Alträsk, Nb</t>
@@ -1238,22 +1220,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:10</t>
+          <t>2017-06-11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,15 +1240,131 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Thomas Andersson</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Thomas Andersson</t>
+          <t>Lars Sundberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122515093</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alträsksvedjan, Alträsk, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>796235</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7304204</v>
+      </c>
+      <c r="S7" t="n">
+        <v>21</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Viktor Persson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51389-2022 artfynd.xlsx
+++ b/artfynd/A 51389-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122515098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122515128</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/34464875</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/45113455</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66220196</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1365,8 +1395,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122515093</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>